--- a/Lab_4/data/partB/param_optimization_process/v100_k10_s200_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v100_k10_s200_results.xlsx
@@ -518,49 +518,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="n">
-        <v>8</v>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>5</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -570,19 +570,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="D3" t="n">
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -594,13 +594,13 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,13 +646,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -674,49 +674,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -726,49 +726,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>2</v>
+      </c>
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -778,49 +778,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N7" t="n">
         <v>7</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -842,22 +842,22 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -872,7 +872,7 @@
         <v>4</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
         <v>2</v>
@@ -894,37 +894,37 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G9" t="n">
         <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="N9" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="n">
         <v>13</v>
-      </c>
-      <c r="D10" t="n">
-        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N11" t="n">
         <v>1</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
         <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>2</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1062,19 +1062,19 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1090,19 +1090,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G13" t="n">
         <v>5</v>
@@ -1117,22 +1117,22 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O13" t="n">
         <v>6</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1145,28 +1145,28 @@
         <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" t="n">
         <v>1</v>
-      </c>
-      <c r="J14" t="n">
-        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -1178,13 +1178,13 @@
         <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -1200,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1215,7 +1215,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -1224,16 +1224,16 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1249,46 +1249,46 @@
         <v>2</v>
       </c>
       <c r="C16" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
         <v>3</v>
       </c>
-      <c r="D16" t="n">
+      <c r="G16" t="n">
+        <v>9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
-      </c>
-      <c r="E16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F16" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" t="n">
-        <v>6</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>4</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3</v>
       </c>
       <c r="K16" t="n">
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M16" t="n">
         <v>2</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -2576,7 +2576,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6248,7 +6248,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6520,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6775,7 +6775,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6945,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7217,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8203,7 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8543,7 +8543,7 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9087,7 +9087,7 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10141,7 +10141,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11773,7 +11773,7 @@
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13541,7 +13541,7 @@
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15003,7 +15003,7 @@
       </c>
       <c r="C806" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15258,7 +15258,7 @@
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="C830" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15496,7 +15496,7 @@
       </c>
       <c r="C835" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C838" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15581,7 +15581,7 @@
       </c>
       <c r="C840" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15683,7 +15683,7 @@
       </c>
       <c r="C846" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="C851" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15853,7 +15853,7 @@
       </c>
       <c r="C856" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15955,7 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16159,7 +16159,7 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16414,7 +16414,7 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16448,7 +16448,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17179,7 +17179,7 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17332,7 +17332,7 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17485,7 +17485,7 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17502,7 +17502,7 @@
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="C959" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17689,7 +17689,7 @@
       </c>
       <c r="C964" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17876,7 +17876,7 @@
       </c>
       <c r="C975" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17944,7 +17944,7 @@
       </c>
       <c r="C979" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="C996" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="C1024" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18726,7 +18726,7 @@
       </c>
       <c r="C1025" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="C1027" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="C1032" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18896,7 +18896,7 @@
       </c>
       <c r="C1035" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18981,7 +18981,7 @@
       </c>
       <c r="C1040" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19423,7 +19423,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19474,7 +19474,7 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="C1072" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19661,7 +19661,7 @@
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19763,7 +19763,7 @@
       </c>
       <c r="C1086" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19797,7 +19797,7 @@
       </c>
       <c r="C1088" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19950,7 @@
       </c>
       <c r="C1097" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20018,7 @@
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20137,7 +20137,7 @@
       </c>
       <c r="C1108" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20222,7 +20222,7 @@
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C1115" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20562,7 +20562,7 @@
       </c>
       <c r="C1133" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20579,7 +20579,7 @@
       </c>
       <c r="C1134" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20732,7 +20732,7 @@
       </c>
       <c r="C1143" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21276,7 +21276,7 @@
       </c>
       <c r="C1175" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -21344,7 +21344,7 @@
       </c>
       <c r="C1179" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21769,7 +21769,7 @@
       </c>
       <c r="C1204" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21820,7 +21820,7 @@
       </c>
       <c r="C1207" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22398,7 +22398,7 @@
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22670,7 +22670,7 @@
       </c>
       <c r="C1257" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22806,7 +22806,7 @@
       </c>
       <c r="C1265" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -23163,7 +23163,7 @@
       </c>
       <c r="C1286" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23214,7 +23214,7 @@
       </c>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24455,7 +24455,7 @@
       </c>
       <c r="C1362" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24676,7 +24676,7 @@
       </c>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24693,7 +24693,7 @@
       </c>
       <c r="C1376" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24812,7 +24812,7 @@
       </c>
       <c r="C1383" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25339,7 +25339,7 @@
       </c>
       <c r="C1414" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25968,7 +25968,7 @@
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26053,7 +26053,7 @@
       </c>
       <c r="C1456" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26155,7 +26155,7 @@
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26529,7 +26529,7 @@
       </c>
       <c r="C1484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26801,7 +26801,7 @@
       </c>
       <c r="C1500" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
